--- a/data/output/reference/analysis_new/comparison_table.xlsx
+++ b/data/output/reference/analysis_new/comparison_table.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,92 +476,97 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
+          <t>T_opt_SE</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>h3_SE</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>h4_SE</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>f1_SE</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>f2</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>f2_SE</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Y_ref</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
           <t>R_squared</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>Total_R_squared</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Adj_R_squared</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>RMS_Imbalance</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>RMS_h_T</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>Imbalance_Ratio</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>n_params</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>f1_SE</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>Y_ref</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>h3_SE</t>
-        </is>
-      </c>
-      <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="inlineStr">
-        <is>
-          <t>h4_SE</t>
-        </is>
-      </c>
-      <c r="W3" s="1" t="inlineStr">
-        <is>
-          <t>f2</t>
-        </is>
-      </c>
-      <c r="X3" s="1" t="inlineStr">
-        <is>
-          <t>T_opt_SE</t>
         </is>
       </c>
     </row>
@@ -586,42 +591,43 @@
       <c r="F4" t="n">
         <v>16.36107330906212</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>0.1962483355988081</v>
       </c>
-      <c r="H4" t="n">
+      <c r="R4" t="n">
         <v>0.1962483355988081</v>
       </c>
-      <c r="I4" t="n">
+      <c r="S4" t="n">
         <v>0.1481428200671316</v>
       </c>
-      <c r="J4" t="n">
+      <c r="T4" t="n">
         <v>0.05809821017601363</v>
       </c>
-      <c r="K4" t="n">
+      <c r="U4" t="n">
         <v>0.03471233235598518</v>
       </c>
-      <c r="L4" t="n">
+      <c r="V4" t="n">
         <v>0.08890243483343716</v>
       </c>
-      <c r="M4" t="n">
+      <c r="W4" t="n">
         <v>0.3904542369511065</v>
       </c>
-      <c r="N4" t="n">
+      <c r="X4" t="n">
         <v>9404</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Y4" t="n">
         <v>532</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,42 +650,43 @@
       <c r="F5" t="n">
         <v>17.0651501975454</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>0.097311977023948</v>
       </c>
-      <c r="H5" t="n">
+      <c r="R5" t="n">
         <v>0.1937889630305749</v>
       </c>
-      <c r="I5" t="n">
+      <c r="S5" t="n">
         <v>0.09122318200815671</v>
       </c>
-      <c r="J5" t="n">
+      <c r="T5" t="n">
         <v>0.0581870286601571</v>
       </c>
-      <c r="K5" t="n">
+      <c r="U5" t="n">
         <v>0.1168972752016664</v>
       </c>
-      <c r="L5" t="n">
+      <c r="V5" t="n">
         <v>0.09434962867605458</v>
       </c>
-      <c r="M5" t="n">
+      <c r="W5" t="n">
         <v>1.238979706036027</v>
       </c>
-      <c r="N5" t="n">
+      <c r="X5" t="n">
         <v>9404</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Y5" t="n">
         <v>64</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -702,42 +709,43 @@
       <c r="F6" t="n">
         <v>17.12967285538169</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>0.09269647451111607</v>
       </c>
-      <c r="H6" t="n">
+      <c r="R6" t="n">
         <v>0.09269647451111607</v>
       </c>
-      <c r="I6" t="n">
+      <c r="S6" t="n">
         <v>0.08657654709079499</v>
       </c>
-      <c r="J6" t="n">
+      <c r="T6" t="n">
         <v>0.06172741781496475</v>
       </c>
-      <c r="K6" t="n">
+      <c r="U6" t="n">
         <v>0.1262835093536402</v>
       </c>
-      <c r="L6" t="n">
+      <c r="V6" t="n">
         <v>0.1057613906048777</v>
       </c>
-      <c r="M6" t="n">
+      <c r="W6" t="n">
         <v>1.194041687910787</v>
       </c>
-      <c r="N6" t="n">
+      <c r="X6" t="n">
         <v>9404</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Y6" t="n">
         <v>64</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -760,42 +768,43 @@
       <c r="F7" t="n">
         <v>14.8455480730791</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>0.09510159303926091</v>
       </c>
-      <c r="H7" t="n">
+      <c r="R7" t="n">
         <v>0.1918148192300179</v>
       </c>
-      <c r="I7" t="n">
+      <c r="S7" t="n">
         <v>0.08899788858117463</v>
       </c>
-      <c r="J7" t="n">
+      <c r="T7" t="n">
         <v>0.05825822548283957</v>
       </c>
-      <c r="K7" t="n">
+      <c r="U7" t="n">
         <v>0.03429573453281316</v>
       </c>
-      <c r="L7" t="n">
+      <c r="V7" t="n">
         <v>0.0006893106420721596</v>
       </c>
-      <c r="M7" t="n">
+      <c r="W7" t="n">
         <v>49.75367046374856</v>
       </c>
-      <c r="N7" t="n">
+      <c r="X7" t="n">
         <v>9404</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Y7" t="n">
         <v>64</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -818,42 +827,43 @@
       <c r="F8" t="n">
         <v>16.71635045540637</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>0.09728045117840756</v>
       </c>
-      <c r="H8" t="n">
+      <c r="R8" t="n">
         <v>0.1937608065867343</v>
       </c>
-      <c r="I8" t="n">
+      <c r="S8" t="n">
         <v>0.09119144351505004</v>
       </c>
-      <c r="J8" t="n">
+      <c r="T8" t="n">
         <v>0.05818804472507394</v>
       </c>
-      <c r="K8" t="n">
+      <c r="U8" t="n">
         <v>0.1150216153070956</v>
       </c>
-      <c r="L8" t="n">
+      <c r="V8" t="n">
         <v>0.09241137099388856</v>
       </c>
-      <c r="M8" t="n">
+      <c r="W8" t="n">
         <v>1.244669504088434</v>
       </c>
-      <c r="N8" t="n">
+      <c r="X8" t="n">
         <v>9404</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Y8" t="n">
         <v>64</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -876,42 +886,43 @@
       <c r="F9" t="n">
         <v>17.36738607572948</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
         <v>0.002061215431057861</v>
       </c>
-      <c r="H9" t="n">
+      <c r="R9" t="n">
         <v>0.1958253408853492</v>
       </c>
-      <c r="I9" t="n">
+      <c r="S9" t="n">
         <v>0.001955074313788274</v>
       </c>
-      <c r="J9" t="n">
+      <c r="T9" t="n">
         <v>0.05811349599399034</v>
       </c>
-      <c r="K9" t="n">
+      <c r="U9" t="n">
         <v>0.1081177533863003</v>
       </c>
-      <c r="L9" t="n">
+      <c r="V9" t="n">
         <v>0.08541058628476624</v>
       </c>
-      <c r="M9" t="n">
+      <c r="W9" t="n">
         <v>1.265858930248136</v>
       </c>
-      <c r="N9" t="n">
+      <c r="X9" t="n">
         <v>9404</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -934,42 +945,43 @@
       <c r="F10" t="n">
         <v>17.62236978977528</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
         <v>0.002364359770347435</v>
       </c>
-      <c r="H10" t="n">
+      <c r="R10" t="n">
         <v>0.0923794829584772</v>
       </c>
-      <c r="I10" t="n">
+      <c r="S10" t="n">
         <v>0.002258250895615599</v>
       </c>
-      <c r="J10" t="n">
+      <c r="T10" t="n">
         <v>0.06173819996266299</v>
       </c>
-      <c r="K10" t="n">
+      <c r="U10" t="n">
         <v>0.1180357460758232</v>
       </c>
-      <c r="L10" t="n">
+      <c r="V10" t="n">
         <v>0.09745596568624323</v>
       </c>
-      <c r="M10" t="n">
+      <c r="W10" t="n">
         <v>1.211170042230519</v>
       </c>
-      <c r="N10" t="n">
+      <c r="X10" t="n">
         <v>9404</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Y10" t="n">
         <v>2</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -992,42 +1004,43 @@
       <c r="F11" t="n">
         <v>12.21422771903372</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
         <v>8.12979295194971e-06</v>
       </c>
-      <c r="H11" t="n">
+      <c r="R11" t="n">
         <v>0.1941708912651051</v>
       </c>
-      <c r="I11" t="n">
+      <c r="S11" t="n">
         <v>-9.822969122219583e-05</v>
       </c>
-      <c r="J11" t="n">
+      <c r="T11" t="n">
         <v>0.05817324448907569</v>
       </c>
-      <c r="K11" t="n">
+      <c r="U11" t="n">
         <v>0.03449857066206617</v>
       </c>
-      <c r="L11" t="n">
+      <c r="V11" t="n">
         <v>0.0001658688349793956</v>
       </c>
-      <c r="M11" t="n">
+      <c r="W11" t="n">
         <v>207.9870559550962</v>
       </c>
-      <c r="N11" t="n">
+      <c r="X11" t="n">
         <v>9404</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Y11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1050,42 +1063,43 @@
       <c r="F12" t="n">
         <v>17.416192164688</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
         <v>0.001989193077229112</v>
       </c>
-      <c r="H12" t="n">
+      <c r="R12" t="n">
         <v>0.195767302704316</v>
       </c>
-      <c r="I12" t="n">
+      <c r="S12" t="n">
         <v>0.001883044299636927</v>
       </c>
-      <c r="J12" t="n">
+      <c r="T12" t="n">
         <v>0.05811559301402835</v>
       </c>
-      <c r="K12" t="n">
+      <c r="U12" t="n">
         <v>0.1050356108734483</v>
       </c>
-      <c r="L12" t="n">
+      <c r="V12" t="n">
         <v>0.08221951081940085</v>
       </c>
-      <c r="M12" t="n">
+      <c r="W12" t="n">
         <v>1.277502259824485</v>
       </c>
-      <c r="N12" t="n">
+      <c r="X12" t="n">
         <v>9404</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Y12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1106,48 +1120,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>3.842056819124606</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4387524313189927</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>19834.64905462024</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.003842981812130386</v>
       </c>
-      <c r="H13" t="n">
+      <c r="R13" t="n">
         <v>0.1972611517730279</v>
       </c>
-      <c r="I13" t="n">
+      <c r="S13" t="n">
         <v>0.003737030204154612</v>
       </c>
-      <c r="J13" t="n">
+      <c r="T13" t="n">
         <v>0.05806159354529941</v>
       </c>
-      <c r="K13" t="n">
+      <c r="U13" t="n">
         <v>0.03457734775573276</v>
       </c>
-      <c r="L13" t="n">
+      <c r="V13" t="n">
         <v>0.003606278114155736</v>
       </c>
-      <c r="M13" t="n">
+      <c r="W13" t="n">
         <v>9.588097939536659</v>
       </c>
-      <c r="N13" t="n">
+      <c r="X13" t="n">
         <v>9404</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Y13" t="n">
         <v>2</v>
       </c>
-      <c r="P13" t="n">
-        <v>3.842056819124606</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.438560291104888</v>
-      </c>
-      <c r="R13" t="n">
-        <v>19834.64905462024</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1170,176 +1185,179 @@
       <c r="F14" t="n">
         <v>15.96594220319622</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
         <v>0.0006526301653105859</v>
       </c>
-      <c r="H14" t="n">
+      <c r="R14" t="n">
         <v>0.2318641432939773</v>
       </c>
-      <c r="I14" t="n">
+      <c r="S14" t="n">
         <v>0.0005463392304206893</v>
       </c>
-      <c r="J14" t="n">
+      <c r="T14" t="n">
         <v>0.05679640272519124</v>
       </c>
-      <c r="K14" t="n">
+      <c r="U14" t="n">
         <v>0.1150812329488553</v>
       </c>
-      <c r="L14" t="n">
+      <c r="V14" t="n">
         <v>0.08937957083046144</v>
       </c>
-      <c r="M14" t="n">
+      <c r="W14" t="n">
         <v>1.287556338429346</v>
       </c>
-      <c r="N14" t="n">
+      <c r="X14" t="n">
         <v>9404</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Y14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6a: Separate Total/Trend Freq LOESS</t>
+          <t>6a: T/Departure LOESS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01434393538220547</v>
+        <v>-0.0005983227318595756</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002792342392550113</v>
+        <v>0.0001600132849117275</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0004548852671901591</v>
+        <v>2.157171200644714e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>8.799599970413198e-05</v>
+        <v>6.494481834597755e-06</v>
       </c>
       <c r="F15" t="n">
-        <v>15.76654204565518</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.003602361397371134</v>
-      </c>
+        <v>13.86822547233977</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.2341314173123862</v>
+        <v>0.001947571160199139</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00328436215100858</v>
+        <v>0.001562883424704369</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05671251901434329</v>
+        <v>-0.002677843283440446</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1121187939703106</v>
+        <v>0.001782466947751997</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004494849409735878</v>
-      </c>
-      <c r="M15" t="n">
-        <v>24.94383765726621</v>
-      </c>
-      <c r="N15" t="n">
+        <v>0.3636454702638412</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>0.0006834344150035143</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2318878205952264</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.0003645035961997722</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.05679552736187585</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.03584654445936403</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.00328352795859354</v>
+      </c>
+      <c r="W15" t="n">
+        <v>10.91708214804374</v>
+      </c>
+      <c r="X15" t="n">
         <v>9404</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Y15" t="n">
         <v>4</v>
       </c>
-      <c r="P15" t="n">
-        <v>15.65690700338264</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>0.01505380144692901</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.002790155540713434</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.000480739952139866</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.806370795693125e-05</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6b: Trend Freq Only LOESS</t>
+          <t>6b: T Only LOESS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0.0006844635212192193</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.0001515296782756766</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2.468652132690624e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>0.0005337351048217975</v>
-      </c>
+        <v>6.234481205815349e-06</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.8631018958757</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.2317727560927865</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0004274315242118742</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05679978123555873</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03898866089301319</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.003209102017874146</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12.14939901438254</v>
-      </c>
-      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0.0001969933183568751</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.231513923730344</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9.065392177309839e-05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.05680934896669887</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.03566596315804338</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.003035021276413694</v>
+      </c>
+      <c r="W16" t="n">
+        <v>11.75147055317772</v>
+      </c>
+      <c r="X16" t="n">
         <v>9404</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Y16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
-        <v>13.71307697902825</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>0.0007390750025716463</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.0001516192366582235</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-2.694781790045852e-05</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.240696940018974e-06</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1360,54 +1378,55 @@
         <v>0.001788409189849119</v>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>-0.0006599182771918821</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0001606975205331707</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.410755317817795e-05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.521146423705503e-06</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4025008597359847</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>13.6869609353229</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
         <v>0.0009630357476998475</v>
       </c>
-      <c r="H17" t="n">
+      <c r="R17" t="n">
         <v>0.2321027326625513</v>
       </c>
-      <c r="I17" t="n">
+      <c r="S17" t="n">
         <v>0.0006441941633641424</v>
       </c>
-      <c r="J17" t="n">
+      <c r="T17" t="n">
         <v>0.05678758132323919</v>
       </c>
-      <c r="K17" t="n">
+      <c r="U17" t="n">
         <v>0.03577778560616989</v>
       </c>
-      <c r="L17" t="n">
+      <c r="V17" t="n">
         <v>0.001229475550203021</v>
       </c>
-      <c r="M17" t="n">
+      <c r="W17" t="n">
         <v>29.10003830516351</v>
       </c>
-      <c r="N17" t="n">
+      <c r="X17" t="n">
         <v>9404</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Y17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>0.4025008597359847</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>-0.0006599182771918821</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.0001606975205331707</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.410755317817795e-05</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.521146423705503e-06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>13.6869609353229</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1431,46 +1450,47 @@
         <v>22.72554333299102</v>
       </c>
       <c r="G18" t="n">
+        <v>0.8695740781503866</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>-0.001713374040142241</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0004478844617833929</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
         <v>0.000919890730125883</v>
       </c>
-      <c r="H18" t="n">
+      <c r="R18" t="n">
         <v>0.2320695697844198</v>
       </c>
-      <c r="I18" t="n">
+      <c r="S18" t="n">
         <v>0.0007073431055604207</v>
       </c>
-      <c r="J18" t="n">
+      <c r="T18" t="n">
         <v>0.05678880754150214</v>
       </c>
-      <c r="K18" t="n">
+      <c r="U18" t="n">
         <v>0.04324500952550513</v>
       </c>
-      <c r="L18" t="n">
+      <c r="V18" t="n">
         <v>0.003397767234918193</v>
       </c>
-      <c r="M18" t="n">
+      <c r="W18" t="n">
         <v>12.7274785279829</v>
       </c>
-      <c r="N18" t="n">
+      <c r="X18" t="n">
         <v>9404</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Y18" t="n">
         <v>3</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>-0.001713374040142241</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.0004478844617833929</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="n">
-        <v>0.8695740781503866</v>
       </c>
     </row>
     <row r="19">
@@ -1495,46 +1515,47 @@
         <v>19.05716642571779</v>
       </c>
       <c r="G19" t="n">
+        <v>1.966204563439507</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>-0.0003587328926053093</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.376419542522856e-05</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
         <v>0.00197013802624002</v>
       </c>
-      <c r="H19" t="n">
+      <c r="R19" t="n">
         <v>0.2328768292328409</v>
       </c>
-      <c r="I19" t="n">
+      <c r="S19" t="n">
         <v>0.001757813834776689</v>
       </c>
-      <c r="J19" t="n">
+      <c r="T19" t="n">
         <v>0.05675895108981834</v>
       </c>
-      <c r="K19" t="n">
+      <c r="U19" t="n">
         <v>0.04023476468751224</v>
       </c>
-      <c r="L19" t="n">
+      <c r="V19" t="n">
         <v>0.003864576995230308</v>
       </c>
-      <c r="M19" t="n">
+      <c r="W19" t="n">
         <v>10.4111691233401</v>
       </c>
-      <c r="N19" t="n">
+      <c r="X19" t="n">
         <v>9404</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Y19" t="n">
         <v>3</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>-0.0003587328926053093</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.376419542522856e-05</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>1.966204563439507</v>
       </c>
     </row>
     <row r="20">
@@ -1544,60 +1565,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0005640870544255437</v>
+        <v>-7.895484254045146e-05</v>
       </c>
       <c r="C20" t="n">
-        <v>9.730656320353033e-05</v>
+        <v>1.222216937087652e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>2.125923039302758e-05</v>
+        <v>3.910779143756866e-06</v>
       </c>
       <c r="E20" t="n">
-        <v>4.136066576658887e-06</v>
+        <v>5.709696907386992e-07</v>
       </c>
       <c r="F20" t="n">
-        <v>13.2668738236768</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.00134971449928134</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.232399948448655</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.00113725831685374</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.05677659040047006</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.036118471531026</v>
-      </c>
+        <v>10.09451564996892</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.003596146085145116</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10.04366081795826</v>
-      </c>
+        <v>-18.87968396262577</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>0.002321579407416507</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2331469602549066</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.002003171400844495</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.0567489567994251</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.0372553519647434</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.004008663910262019</v>
+      </c>
+      <c r="W20" t="n">
+        <v>9.293708028096638</v>
+      </c>
+      <c r="X20" t="n">
         <v>9404</v>
       </c>
-      <c r="O20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.944569865098343</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.099214204457635</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1618,36 +1640,37 @@
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0.1942461901590998</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1942461901590998</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.1462133114791543</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.05817052649139099</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>9404</v>
-      </c>
-      <c r="O21" t="n">
-        <v>530</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>0.1942461901590998</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1942461901590998</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1462133114791543</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.05817052649139099</v>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>9404</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>530</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1668,36 +1691,37 @@
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>0.1941643399880358</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1941643399880358</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1458378186120506</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.05817348095873405</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>9404</v>
-      </c>
-      <c r="O22" t="n">
-        <v>533</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0.1941643399880358</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.1941643399880358</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1458378186120506</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.05817348095873405</v>
+      </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>9404</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>533</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2446,17 +2470,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6a: Separate Total/Trend Freq LOESS</t>
+          <t>6a: T/Departure LOESS</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.004199558365046725</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003209814507527086</v>
+        <v>0.0003692375194954719</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2104195631821776</v>
+        <v>0.0005501517673825498</v>
       </c>
       <c r="E13" t="n">
         <v>0.1313109233784202</v>
@@ -2465,37 +2489,37 @@
         <v>0.0902284557189722</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9633068901429428</v>
+        <v>0.7680835766183043</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02347582869539261</v>
+        <v>6.067085096090975e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.002679972921750731</v>
+        <v>-0.0005788579653456965</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.001039378942040119</v>
+        <v>0.0001376463235318428</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02306170289261184</v>
+        <v>-6.684025365415225e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01957867825295185</v>
+        <v>-0.002048628367146893</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0001729021036977103</v>
+        <v>0.0001237816489203062</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4078846493099063</v>
+        <v>-0.0003593037825285435</v>
       </c>
       <c r="O13" t="n">
         <v>-0.01197861020266722</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.007075577148554012</v>
+        <v>0.01245061451513967</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01284508704100953</v>
+        <v>0.01171718223021498</v>
       </c>
       <c r="R13" t="n">
         <v>0.9999999999999999</v>
@@ -2504,17 +2528,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6b: Trend Freq Only LOESS</t>
+          <t>6b: T Only LOESS</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.004199558365046725</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0008827658228741158</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0008827658228741158</v>
+        <v>0.0007213065039925824</v>
       </c>
       <c r="E14" t="n">
         <v>0.1313109233784202</v>
@@ -2523,40 +2547,40 @@
         <v>0.0902284557189722</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7686374927199605</v>
+        <v>0.7684395581214428</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.001765531645748232</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.00269181661424755</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000103754138095565</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001324059623661161</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00269181661424755</v>
+        <v>-0.002348288874104858</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.000103754138095565</v>
+        <v>0.0001419102929562718</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.001324059623661161</v>
+        <v>-0.0005233719054746017</v>
       </c>
       <c r="O14" t="n">
         <v>-0.01197861020266722</v>
       </c>
       <c r="P14" t="n">
-        <v>0.009823128182647082</v>
+        <v>0.01217141705675195</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01197861020266713</v>
+        <v>0.01183669990971086</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2743,10 +2767,10 @@
         <v>0.004199558365046725</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0007633838272887766</v>
+        <v>0.003540982370711801</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000611328601898242</v>
+        <v>4.660970426674944e-05</v>
       </c>
       <c r="E18" t="n">
         <v>0.1313109233784202</v>
@@ -2755,40 +2779,40 @@
         <v>0.0902284557189722</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7674969869035289</v>
+        <v>0.7649941515422749</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0004771767433617025</v>
+        <v>0.0002345548349330605</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001388447279139684</v>
+        <v>-0.002335319599776779</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0004341836990552625</v>
+        <v>-0.0006440932594343442</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0001890779290036804</v>
+        <v>-0.0002415576812606537</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.002412304691090885</v>
+        <v>-0.0008213697989417622</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001023961551994955</v>
+        <v>4.570557946635196e-05</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.000522305427113384</v>
+        <v>6.275194903471676e-05</v>
       </c>
       <c r="O18" t="n">
         <v>-0.01197861020266722</v>
       </c>
       <c r="P18" t="n">
-        <v>0.01362388015287765</v>
+        <v>0.01297981758136564</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01144203034841237</v>
+        <v>0.01257699788263511</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
